--- a/AAII_Financials/Yearly/FGPR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FGPR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>FGPR</t>
   </si>
@@ -656,209 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44773</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44408</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44043</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43677</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43312</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42947</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42582</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42216</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41851</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41486</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1864000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1938300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1837100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2026500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2114500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1754300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1497800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1684400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2073100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1930300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2039400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2024400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2405900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1975500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>840100</v>
+      </c>
+      <c r="E9" s="3">
         <v>915500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>854000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1018300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1184900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>892800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>684500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>913900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1297600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1190400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1163000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1224500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1604400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1236700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1024000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1022800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>983100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1008200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>929700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>861600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>813300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>770500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>775500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>739800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>876400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>799900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>801500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>738800</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +889,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +934,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +982,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E14" s="3">
         <v>128000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-6600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>117100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>45300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>197400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>658100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>21200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E15" s="3">
         <v>98400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>98500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>93400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>89900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>85400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>80500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>78800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>101800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>103400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>150500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>98600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>84200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>83300</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1098,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1660900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1720300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1629200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1787100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1876100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1536200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1341200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1560400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1967700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1834900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2573600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1893900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2282600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1827900</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>203100</v>
+      </c>
+      <c r="E18" s="3">
         <v>218100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>207900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>239400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>238500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>218100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>156600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>124000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>105400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>95400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-534200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>130500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>123200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>147600</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1214,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>312500</v>
+      </c>
+      <c r="E21" s="3">
         <v>319400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>310900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>335400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>333200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>307700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>236600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>203200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>208200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>192400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-390800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>221500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>197500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>212800</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E22" s="3">
         <v>108100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>98200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>97700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>100100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>173600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>193000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>177600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>168500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>144700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>130800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>93200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>77000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>70500</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>111400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>138600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>149800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-68400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-82200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-64200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-259500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-55600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-672100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>29800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>59000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1000</v>
       </c>
       <c r="G24" s="3">
         <v>1000</v>
       </c>
       <c r="H24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1499,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>110700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>137600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>148900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-69100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-83000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-64500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-256800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-54500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-672000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>30100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>33700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>57200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-79500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-55700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-91800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-81700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-63600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-252000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-53700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-658800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>29300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>32900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>55900</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1643,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1630,9 +1691,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1739,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1787,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>18100</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>109100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>135500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>146500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-67700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-81700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-63600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-252000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-53700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-658800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>29300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>32900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>55900</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1931,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>109100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>135500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>146500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-67700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-81700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-63600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-252000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-53700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-658800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>29300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>32900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>55900</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44773</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44408</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44043</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43677</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43312</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42947</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42582</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42216</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41851</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41486</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2055,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,53 +2075,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E41" s="3">
         <v>96900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>113500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>126200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>147500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>270500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>238000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>119300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2078,189 +2168,204 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E43" s="3">
         <v>127500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>159400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>150400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>131600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>101400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>107600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>126100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>165100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>149600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>196900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>178600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>131800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E44" s="3">
         <v>87800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>96000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>98100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>115200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>88400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>72700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>80500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>83700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>92600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>90600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>96800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>146000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>117100</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>17000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>73800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>117100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>64300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>25600</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>291900</v>
+      </c>
+      <c r="E46" s="3">
         <v>342700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>375200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>435900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>498100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>619000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>543800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>241400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>363900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>296800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>285100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>365600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>364900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>281000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2288,11 +2393,11 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>32500</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
@@ -2303,99 +2408,108 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>626700</v>
+      </c>
+      <c r="E48" s="3">
         <v>679500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>677400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>697500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>707500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>704600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>739800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>596700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>557700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>731900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>774700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>965200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>611800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>589700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>356400</v>
+      </c>
+      <c r="E49" s="3">
         <v>363600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>369200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>363600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>354700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>347700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>351200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>355800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>367000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>507200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>536300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1058800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>549400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>442900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2552,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2600,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E52" s="3">
         <v>30900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>37000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>47800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>38600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>52300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>46400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>87200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>48100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>46200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2696,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1364800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1416700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1458800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1531400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1608100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1729600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1668200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1263000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1363300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1610000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1683300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2437700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1572300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1356000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2767,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2787,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E57" s="3">
         <v>31100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>57600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>47900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>46800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>85600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>67900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>84000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>69400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>49100</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E58" s="3">
         <v>680700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>33700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>33400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>34200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>34500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>895400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>736800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>93200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>128800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>165300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>145300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>164100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>132100</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>171800</v>
+      </c>
+      <c r="E59" s="3">
         <v>128100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>103500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>111500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>136500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>170200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>73500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>81900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>86200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>126200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>129000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>180700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>121500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>121100</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>312400</v>
+      </c>
+      <c r="E60" s="3">
         <v>914500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>242800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>259300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>303800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>320900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1089900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>908400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>279600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>340600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>362200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>410000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>355000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>302300</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2130400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1518100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2155700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2161400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2173900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2198600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1768900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1457000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2078600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1995800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1941300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1778100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1292200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1106900</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E62" s="3">
         <v>13300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>18200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>33200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>39500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>31600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>42000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>36700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33400</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3120,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3168,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3216,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2494500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2445800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2408400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2430200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2495900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2552700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2876500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2401900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2397800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2363500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2330400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2234000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1684600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1443600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3287,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3332,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3380,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3246,23 +3414,26 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>-67000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>-65800</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>-57000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>-60700</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>-60400</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,9 +3476,12 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3335,8 +3509,8 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
+      <c r="L72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M72" s="3">
         <v>0</v>
@@ -3350,9 +3524,12 @@
       <c r="P72" s="3">
         <v>0</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3572,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3620,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3668,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1051100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-949800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-871900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-821000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-808900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-742900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1128800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1060800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-958000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-686600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-581300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>260800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-51700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3764,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44773</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44408</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44043</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43677</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43312</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42947</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42582</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42216</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41851</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41486</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>109100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>135500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>146500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-67700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-81700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-63600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-252000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-53700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-658800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>29300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>32900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>55900</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3888,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E83" s="3">
         <v>90500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>89200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>84800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>81800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>76600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>71400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>64300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>70500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>103400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>150500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>98600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>84200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>83300</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3981,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4029,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4077,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4125,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4173,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E89" s="3">
         <v>136300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>245600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>212300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>160500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>206400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>130400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>74100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>127300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>194300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>203100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>125700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>210100</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4244,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-80000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-70900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-88900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-96700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-61200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-107500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-118800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-84900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-50500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-117500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-72500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-52600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4337,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4385,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-75500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-80800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-85000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-110800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-111800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-61000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-71300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-124300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>49500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-45500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-115900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-708000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-210100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-68100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4456,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>100000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>50000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>100000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>9700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>38900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-79700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-204200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-167100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-160900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4549,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4597,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,54 +4645,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-125600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-82800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-173700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-122900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-171900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-197300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>263600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-10100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-81000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-81200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>504300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>86400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-143800</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4477,8 +4726,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4487,57 +4736,63 @@
         <v>0</v>
       </c>
       <c r="O101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-48500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-27300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-123200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-51800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>322700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-108300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>113600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
